--- a/artfynd/A 1339-2025 artfynd.xlsx
+++ b/artfynd/A 1339-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126336995</v>
+        <v>126336096</v>
       </c>
       <c r="B2" t="n">
-        <v>78738</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hobben, Hobben, Ly lm</t>
+          <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563552</v>
+        <v>563399</v>
       </c>
       <c r="R2" t="n">
-        <v>7305885</v>
+        <v>7306122</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,12 +757,13 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog med relativt mycket silvervedsrester lämnade efter dimensionsavverkningarna</t>
+          <t>Grannaturskog med inslag av grova tallar, tidigare brandpräglad biotop</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -777,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126337011</v>
+        <v>126336132</v>
       </c>
       <c r="B3" t="n">
-        <v>92727</v>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,34 +792,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2079</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hobben, Hobben, Ly lm</t>
+          <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563555</v>
+        <v>563361</v>
       </c>
       <c r="R3" t="n">
-        <v>7305865</v>
+        <v>7306129</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,12 +863,13 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog med relativt mycket silvervedsrester lämnade efter dimensionsavverkningarna</t>
+          <t>Grannaturskog med inslag av grova tallar, tidigare brandpräglad biotop</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -879,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126337463</v>
+        <v>126339287</v>
       </c>
       <c r="B4" t="n">
-        <v>91263</v>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,34 +898,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hobben, Hobben, Ly lm</t>
+          <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563471</v>
+        <v>563049</v>
       </c>
       <c r="R4" t="n">
-        <v>7305795</v>
+        <v>7306120</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,7 +971,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Lågproduktiv gransumpskog mellan hällmarkstallskogar</t>
+          <t>Produktiv, grov och bitvis frodig grannaturskog med stora mängder död ved, mellan lågproduktiva hällmarkstallskogar</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -981,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126338580</v>
+        <v>126339468</v>
       </c>
       <c r="B5" t="n">
-        <v>91263</v>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,34 +1000,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hobben, Hobben, Ly lm</t>
+          <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563192</v>
+        <v>563057</v>
       </c>
       <c r="R5" t="n">
-        <v>7305876</v>
+        <v>7306163</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126336991</v>
+        <v>126338163</v>
       </c>
       <c r="B6" t="n">
-        <v>79598</v>
+        <v>79406</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,21 +1102,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1118,10 +1126,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563552</v>
+        <v>563363</v>
       </c>
       <c r="R6" t="n">
-        <v>7305885</v>
+        <v>7305729</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1167,7 +1175,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog med relativt mycket silvervedsrester lämnade efter dimensionsavverkningarna</t>
+          <t>Lågproduktiv gransumpskog mellan hällmarkstallskogar</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1185,48 +1193,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126336096</v>
+        <v>126339168</v>
       </c>
       <c r="B7" t="n">
-        <v>91541</v>
+        <v>92721</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>918</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563399</v>
+        <v>563023</v>
       </c>
       <c r="R7" t="n">
-        <v>7306122</v>
+        <v>7306110</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1267,13 +1272,12 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Grannaturskog med inslag av grova tallar, tidigare brandpräglad biotop</t>
+          <t>Produktiv, grov och bitvis frodig grannaturskog med stora mängder död ved, mellan lågproduktiva hällmarkstallskogar</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1291,10 +1295,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126337678</v>
+        <v>126338565</v>
       </c>
       <c r="B8" t="n">
-        <v>75075</v>
+        <v>91905</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,21 +1306,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1326,10 +1330,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563500</v>
+        <v>563208</v>
       </c>
       <c r="R8" t="n">
-        <v>7305702</v>
+        <v>7305867</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1375,7 +1379,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Lågproduktiv gransumpskog mellan hällmarkstallskogar</t>
+          <t>Produktiv, grov och bitvis frodig grannaturskog med stora mängder död ved, mellan lågproduktiva hällmarkstallskogar</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1393,10 +1397,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126339688</v>
+        <v>126339437</v>
       </c>
       <c r="B9" t="n">
-        <v>91263</v>
+        <v>92097</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1404,21 +1408,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1588</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1428,10 +1432,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563214</v>
+        <v>563049</v>
       </c>
       <c r="R9" t="n">
-        <v>7306068</v>
+        <v>7306162</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,10 +1499,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126339287</v>
+        <v>126337011</v>
       </c>
       <c r="B10" t="n">
-        <v>91541</v>
+        <v>91962</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1506,34 +1510,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>2079</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
+          <t>Hobben, Hobben, Ly lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563049</v>
+        <v>563555</v>
       </c>
       <c r="R10" t="n">
-        <v>7306120</v>
+        <v>7305865</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1579,7 +1583,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Produktiv, grov och bitvis frodig grannaturskog med stora mängder död ved, mellan lågproduktiva hällmarkstallskogar</t>
+          <t>Hällmarkstallskog med relativt mycket silvervedsrester lämnade efter dimensionsavverkningarna</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1597,45 +1601,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126338565</v>
+        <v>126339384</v>
       </c>
       <c r="B11" t="n">
-        <v>91241</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hobben, Hobben, Ly lm</t>
+          <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563208</v>
+        <v>563050</v>
       </c>
       <c r="R11" t="n">
-        <v>7305867</v>
+        <v>7306147</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,10 +1703,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126339384</v>
+        <v>126337678</v>
       </c>
       <c r="B12" t="n">
-        <v>78980</v>
+        <v>83307</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1710,34 +1714,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
+          <t>Hobben, Hobben, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563050</v>
+        <v>563500</v>
       </c>
       <c r="R12" t="n">
-        <v>7306147</v>
+        <v>7305702</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1783,7 +1787,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Produktiv, grov och bitvis frodig grannaturskog med stora mängder död ved, mellan lågproduktiva hällmarkstallskogar</t>
+          <t>Lågproduktiv gransumpskog mellan hällmarkstallskogar</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1801,10 +1805,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126340112</v>
+        <v>126336995</v>
       </c>
       <c r="B13" t="n">
-        <v>91263</v>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1812,34 +1816,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Räftmyran, Räftmyran, Ly lm</t>
+          <t>Hobben, Hobben, Ly lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563520</v>
+        <v>563552</v>
       </c>
       <c r="R13" t="n">
-        <v>7306073</v>
+        <v>7305885</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1885,7 +1889,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Produktiv, grov och bitvis frodig grannaturskog med stora mängder död ved, mellan lågproduktiva hällmarkstallskogar</t>
+          <t>Hällmarkstallskog med relativt mycket silvervedsrester lämnade efter dimensionsavverkningarna</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1903,10 +1907,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126339468</v>
+        <v>126336991</v>
       </c>
       <c r="B14" t="n">
-        <v>91541</v>
+        <v>79946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1914,34 +1918,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
+          <t>Hobben, Hobben, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563057</v>
+        <v>563552</v>
       </c>
       <c r="R14" t="n">
-        <v>7306163</v>
+        <v>7305885</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1987,7 +1991,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Produktiv, grov och bitvis frodig grannaturskog med stora mängder död ved, mellan lågproduktiva hällmarkstallskogar</t>
+          <t>Hällmarkstallskog med relativt mycket silvervedsrester lämnade efter dimensionsavverkningarna</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2002,312 +2006,6 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>126339168</v>
-      </c>
-      <c r="B15" t="n">
-        <v>92032</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>918</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Tajgaskinn</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Laurilia sulcata</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Burt) Pouzar</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>563023</v>
-      </c>
-      <c r="R15" t="n">
-        <v>7306110</v>
-      </c>
-      <c r="S15" t="n">
-        <v>10</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Produktiv, grov och bitvis frodig grannaturskog med stora mängder död ved, mellan lågproduktiva hällmarkstallskogar</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>126338163</v>
-      </c>
-      <c r="B16" t="n">
-        <v>79059</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>864</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Knottrig blåslav</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Hypogymnia bitteri</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Hobben, Hobben, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>563363</v>
-      </c>
-      <c r="R16" t="n">
-        <v>7305729</v>
-      </c>
-      <c r="S16" t="n">
-        <v>10</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Lågproduktiv gransumpskog mellan hällmarkstallskogar</t>
-        </is>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>126339437</v>
-      </c>
-      <c r="B17" t="n">
-        <v>91420</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>1588</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Violmussling</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Trichaptum laricinum</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Ryvarden</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>563049</v>
-      </c>
-      <c r="R17" t="n">
-        <v>7306162</v>
-      </c>
-      <c r="S17" t="n">
-        <v>10</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Produktiv, grov och bitvis frodig grannaturskog med stora mängder död ved, mellan lågproduktiva hällmarkstallskogar</t>
-        </is>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1339-2025 artfynd.xlsx
+++ b/artfynd/A 1339-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126336096</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126336132</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126339287</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126339468</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1190,6 +1215,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126338163</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1292,6 +1322,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126339168</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1394,6 +1429,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126338565</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1496,6 +1536,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126339437</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1598,6 +1643,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126337011</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1700,6 +1750,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126339384</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1802,6 +1857,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126337678</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1904,6 +1964,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126336995</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2006,8 +2071,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126336991</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>